--- a/output/2026-10-03_08_Malesia_Perak_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-03_08_Malesia_Perak_ATEX_Equipment_Services.xlsx
@@ -484,10 +484,9 @@
           <t>+60 3 7728 6250</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stockist/value-add manufacturer di prodotti antideflagranti, partner di CEAG (explosion-proof), Mennekes, Rittal, Mankenberg; certificazione ISO 9001:2015. Sedi confermate: Petaling Jaya (HQ), Sunway Damansara, Kemaman, Bintulu, Miri, Penang. Nessuna sede in Perak confermata.</t>
+          <t>Stockist/value-add manufacturer di prodotti antideflagranti, partner di CEAG (explosion-proof), Mennekes, Rittal, Mankenberg; certificazione ISO 9001:2015. Sedi confermate: Petaling Jaya (HQ), Sunway Damansara, Kemaman, Bintulu, Miri, Penang. Nessuna sede in Perak confermata. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -517,11 +516,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/stockista dal 2004 di apparecchi di illuminazione ed equipaggiamenti elettrici per aree pericolose, certificati ATEX/IECEx/IEC/CENELEC/CSA/UL/FM. Sede: 15B Jalan Anggerik Vanilla N31/N, Kota Kemuning, Shah Alam, Selangor. Distributore nazionale, nessuna sede Perak confermata.</t>
+          <t>Distributore/stockista dal 2004 di apparecchi di illuminazione ed equipaggiamenti elettrici per aree pericolose, certificati ATEX/IECEx/IEC/CENELEC/CSA/UL/FM. Sede: 15B Jalan Anggerik Vanilla N31/N, Kota Kemuning, Shah Alam, Selangor. Distributore nazionale, nessuna sede Perak confermata. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,10 +553,9 @@
           <t>+604-502 3882</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gruppo regionale PPE/sicurezza industriale incl. prodotti explosion-proof. Pagina ufficiale "Our Locations" conferma filiali in Penang (HQ), Selangor, Johor, Melaka, Pahang, Sabah, Sarawak - nessuna filiale in Perak confermata ufficialmente.</t>
+          <t>Gruppo regionale PPE/sicurezza industriale incl. prodotti explosion-proof. Pagina ufficiale "Our Locations" conferma filiali in Penang (HQ), Selangor, Johor, Melaka, Pahang, Sabah, Sarawak - nessuna filiale in Perak confermata ufficialmente. [DUPLICATO — vedi anche: 2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -574,7 +570,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Selangor (Puchong, HQ) - copertura Perak non confermata, distributore nazionale</t>
@@ -585,11 +580,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore nazionale di prodotti per aree pericolose/ATEX (cable glands, fusibili industriali, prese industriali, lampade antideflagranti), certificati ATEX/IECEx/IEC/CSA. Costituita luglio 1982, sede 14 &amp; 16 Jalan TPP 5/2, Taman Perindustrian Puchong, Selangor (SSM No. 87458A). Nessun sito web ufficiale reperito; nessuna sede in Perak confermata.</t>
+          <t>Distributore nazionale di prodotti per aree pericolose/ATEX (cable glands, fusibili industriali, prese industriali, lampade antideflagranti), certificati ATEX/IECEx/IEC/CSA. Costituita luglio 1982, sede 14 &amp; 16 Jalan TPP 5/2, Taman Perindustrian Puchong, Selangor (SSM No. 87458A). Nessun sito web ufficiale reperito; nessuna sede in Perak confermata. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -636,7 +629,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
